--- a/output/yearly_total_coral_cover_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_15_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.263564700508981</v>
+        <v>1.254738788647802</v>
       </c>
       <c r="C3" t="n">
-        <v>4.604776560339245</v>
+        <v>4.665998347176076</v>
       </c>
       <c r="D3" t="n">
-        <v>6.036231674849463</v>
+        <v>6.118806474253662</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90457293569769</v>
+        <v>12.03954361007754</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.405356466560938</v>
+        <v>1.383882101223085</v>
       </c>
       <c r="C4" t="n">
-        <v>5.111710611609705</v>
+        <v>5.207486383713157</v>
       </c>
       <c r="D4" t="n">
-        <v>6.352994422952646</v>
+        <v>6.337175740613693</v>
       </c>
       <c r="E4" t="n">
-        <v>12.87006150112329</v>
+        <v>12.92854422554993</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.591289863726719</v>
+        <v>1.562536067413123</v>
       </c>
       <c r="C5" t="n">
-        <v>5.77653279574778</v>
+        <v>5.910390070017415</v>
       </c>
       <c r="D5" t="n">
-        <v>6.729413830119955</v>
+        <v>6.651622027730506</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09723648959445</v>
+        <v>14.12454816516104</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.799278673129322</v>
+        <v>1.767787355893038</v>
       </c>
       <c r="C6" t="n">
-        <v>6.633371043608803</v>
+        <v>6.801548908738034</v>
       </c>
       <c r="D6" t="n">
-        <v>7.131643630771334</v>
+        <v>6.953268223296459</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56429334750946</v>
+        <v>15.52260448792753</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.023738305693486</v>
+        <v>2.00816618165532</v>
       </c>
       <c r="C7" t="n">
-        <v>7.717211969331602</v>
+        <v>7.857217418271223</v>
       </c>
       <c r="D7" t="n">
-        <v>7.534325534160815</v>
+        <v>7.422962084426147</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2752758091859</v>
+        <v>17.28834568435269</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.234874332635879</v>
+        <v>1.248975029854236</v>
       </c>
       <c r="C8" t="n">
-        <v>5.581103160914623</v>
+        <v>5.563332781143763</v>
       </c>
       <c r="D8" t="n">
-        <v>5.77700764447392</v>
+        <v>5.665450948586952</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59298513802442</v>
+        <v>12.47775875958495</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.537456986597319</v>
+        <v>1.582836250508233</v>
       </c>
       <c r="C9" t="n">
-        <v>7.101871913392308</v>
+        <v>6.946939106289092</v>
       </c>
       <c r="D9" t="n">
-        <v>6.295504395377606</v>
+        <v>6.186800090221087</v>
       </c>
       <c r="E9" t="n">
-        <v>14.93483329536723</v>
+        <v>14.71657544701841</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.847286300922632</v>
+        <v>1.926504956524857</v>
       </c>
       <c r="C10" t="n">
-        <v>8.901142421049679</v>
+        <v>8.575544739500083</v>
       </c>
       <c r="D10" t="n">
-        <v>6.868648418396029</v>
+        <v>6.697470915677155</v>
       </c>
       <c r="E10" t="n">
-        <v>17.61707714036834</v>
+        <v>17.19952061170209</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.150829072552609</v>
+        <v>2.271500843937245</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83169492563284</v>
+        <v>10.33235717249793</v>
       </c>
       <c r="D11" t="n">
-        <v>7.38148266600919</v>
+        <v>7.24604591378696</v>
       </c>
       <c r="E11" t="n">
-        <v>20.36400666419464</v>
+        <v>19.84990393022214</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.445600740488016</v>
+        <v>2.59990700823906</v>
       </c>
       <c r="C12" t="n">
-        <v>12.78813162075256</v>
+        <v>12.21785924078255</v>
       </c>
       <c r="D12" t="n">
-        <v>7.831180068456635</v>
+        <v>7.78174485777966</v>
       </c>
       <c r="E12" t="n">
-        <v>23.06491242969721</v>
+        <v>22.59951110680127</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.710186585594921</v>
+        <v>2.894431059402691</v>
       </c>
       <c r="C13" t="n">
-        <v>14.7004748569612</v>
+        <v>14.11813979775908</v>
       </c>
       <c r="D13" t="n">
-        <v>8.204918871068166</v>
+        <v>8.219026438267907</v>
       </c>
       <c r="E13" t="n">
-        <v>25.61558031362429</v>
+        <v>25.23159729542968</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.557542732787565</v>
+        <v>1.651741425010046</v>
       </c>
       <c r="C14" t="n">
-        <v>10.03425675304284</v>
+        <v>9.827107987446764</v>
       </c>
       <c r="D14" t="n">
-        <v>6.207256939733139</v>
+        <v>6.244200105843946</v>
       </c>
       <c r="E14" t="n">
-        <v>17.79905642556355</v>
+        <v>17.72304951830075</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.574693865180756</v>
+        <v>1.67375220853926</v>
       </c>
       <c r="C15" t="n">
-        <v>11.00167094080765</v>
+        <v>10.80201291019498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.184401853178272</v>
+        <v>6.255774911277015</v>
       </c>
       <c r="E15" t="n">
-        <v>18.76076665916668</v>
+        <v>18.73154003001125</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.810411488970416</v>
+        <v>1.91384842708986</v>
       </c>
       <c r="C16" t="n">
-        <v>13.00175608623855</v>
+        <v>12.81667700903394</v>
       </c>
       <c r="D16" t="n">
-        <v>6.588381215998792</v>
+        <v>6.730911347701344</v>
       </c>
       <c r="E16" t="n">
-        <v>21.40054879120776</v>
+        <v>21.46143678382514</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.442972775701962</v>
+        <v>1.518852055763198</v>
       </c>
       <c r="C17" t="n">
-        <v>11.98871026518035</v>
+        <v>11.84025037734415</v>
       </c>
       <c r="D17" t="n">
-        <v>6.061634302762209</v>
+        <v>6.227598752165131</v>
       </c>
       <c r="E17" t="n">
-        <v>19.49331734364452</v>
+        <v>19.58670118527248</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.630339325057466</v>
+        <v>1.705001237965436</v>
       </c>
       <c r="C18" t="n">
-        <v>13.92767179854484</v>
+        <v>13.81283676957909</v>
       </c>
       <c r="D18" t="n">
-        <v>6.432410958225102</v>
+        <v>6.591660253330977</v>
       </c>
       <c r="E18" t="n">
-        <v>21.99042208182741</v>
+        <v>22.10949826087551</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.622063191910665</v>
+        <v>1.683520598196516</v>
       </c>
       <c r="C19" t="n">
-        <v>14.829976478564</v>
+        <v>14.74750967140727</v>
       </c>
       <c r="D19" t="n">
-        <v>6.491777241900906</v>
+        <v>6.672644621454297</v>
       </c>
       <c r="E19" t="n">
-        <v>22.94381691237557</v>
+        <v>23.10367489105808</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.788714864706561</v>
+        <v>1.847020860861779</v>
       </c>
       <c r="C20" t="n">
-        <v>16.88462716139694</v>
+        <v>16.82918786853812</v>
       </c>
       <c r="D20" t="n">
-        <v>6.908313157858744</v>
+        <v>7.093195885522502</v>
       </c>
       <c r="E20" t="n">
-        <v>25.58165518396224</v>
+        <v>25.7694046149224</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.054436304269244</v>
+        <v>1.081738707924348</v>
       </c>
       <c r="C21" t="n">
-        <v>12.21025145212069</v>
+        <v>12.22247421103856</v>
       </c>
       <c r="D21" t="n">
-        <v>5.748554959877902</v>
+        <v>5.920007378947564</v>
       </c>
       <c r="E21" t="n">
-        <v>19.01324271626783</v>
+        <v>19.22422029791047</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_15_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254738788647802</v>
+        <v>1.248386881001325</v>
       </c>
       <c r="C3" t="n">
-        <v>4.665998347176076</v>
+        <v>4.604609663229524</v>
       </c>
       <c r="D3" t="n">
-        <v>6.118806474253662</v>
+        <v>6.193056053125848</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03954361007754</v>
+        <v>12.0460525973567</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.383882101223085</v>
+        <v>1.361261519737573</v>
       </c>
       <c r="C4" t="n">
-        <v>5.207486383713157</v>
+        <v>5.058195993700082</v>
       </c>
       <c r="D4" t="n">
-        <v>6.337175740613693</v>
+        <v>6.511907065912051</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92854422554993</v>
+        <v>12.93136457934971</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.562536067413123</v>
+        <v>1.515753976986745</v>
       </c>
       <c r="C5" t="n">
-        <v>5.910390070017415</v>
+        <v>5.613911787456547</v>
       </c>
       <c r="D5" t="n">
-        <v>6.651622027730506</v>
+        <v>6.872946848635062</v>
       </c>
       <c r="E5" t="n">
-        <v>14.12454816516104</v>
+        <v>14.00261261307835</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.767787355893038</v>
+        <v>1.684635702008681</v>
       </c>
       <c r="C6" t="n">
-        <v>6.801548908738034</v>
+        <v>6.319497794675752</v>
       </c>
       <c r="D6" t="n">
-        <v>6.953268223296459</v>
+        <v>7.382701257708938</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52260448792753</v>
+        <v>15.38683475439337</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.00816618165532</v>
+        <v>1.879883083389651</v>
       </c>
       <c r="C7" t="n">
-        <v>7.857217418271223</v>
+        <v>7.159556716972675</v>
       </c>
       <c r="D7" t="n">
-        <v>7.422962084426147</v>
+        <v>7.916481819011974</v>
       </c>
       <c r="E7" t="n">
-        <v>17.28834568435269</v>
+        <v>16.9559216193743</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.248975029854236</v>
+        <v>1.119046003421087</v>
       </c>
       <c r="C8" t="n">
-        <v>5.563332781143763</v>
+        <v>4.82267820283136</v>
       </c>
       <c r="D8" t="n">
-        <v>5.665450948586952</v>
+        <v>6.171691336829056</v>
       </c>
       <c r="E8" t="n">
-        <v>12.47775875958495</v>
+        <v>12.1134155430815</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.582836250508233</v>
+        <v>1.381155720613277</v>
       </c>
       <c r="C9" t="n">
-        <v>6.946939106289092</v>
+        <v>5.852181396561777</v>
       </c>
       <c r="D9" t="n">
-        <v>6.186800090221087</v>
+        <v>6.881097350875271</v>
       </c>
       <c r="E9" t="n">
-        <v>14.71657544701841</v>
+        <v>14.11443446805032</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.926504956524857</v>
+        <v>1.656901115559408</v>
       </c>
       <c r="C10" t="n">
-        <v>8.575544739500083</v>
+        <v>7.048126988456517</v>
       </c>
       <c r="D10" t="n">
-        <v>6.697470915677155</v>
+        <v>7.604633049674902</v>
       </c>
       <c r="E10" t="n">
-        <v>17.19952061170209</v>
+        <v>16.30966115369083</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.271500843937245</v>
+        <v>1.922675323960846</v>
       </c>
       <c r="C11" t="n">
-        <v>10.33235717249793</v>
+        <v>8.391252553998203</v>
       </c>
       <c r="D11" t="n">
-        <v>7.24604591378696</v>
+        <v>8.240671073489988</v>
       </c>
       <c r="E11" t="n">
-        <v>19.84990393022214</v>
+        <v>18.55459895144904</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.59990700823906</v>
+        <v>2.191729304459689</v>
       </c>
       <c r="C12" t="n">
-        <v>12.21785924078255</v>
+        <v>9.849763675611468</v>
       </c>
       <c r="D12" t="n">
-        <v>7.78174485777966</v>
+        <v>9.052723974763689</v>
       </c>
       <c r="E12" t="n">
-        <v>22.59951110680127</v>
+        <v>21.09421695483485</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.894431059402691</v>
+        <v>2.454548798934983</v>
       </c>
       <c r="C13" t="n">
-        <v>14.11813979775908</v>
+        <v>11.40906844343753</v>
       </c>
       <c r="D13" t="n">
-        <v>8.219026438267907</v>
+        <v>9.727246039231908</v>
       </c>
       <c r="E13" t="n">
-        <v>25.23159729542968</v>
+        <v>23.59086328160442</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.651741425010046</v>
+        <v>1.424780990742269</v>
       </c>
       <c r="C14" t="n">
-        <v>9.827107987446764</v>
+        <v>8.083612421997813</v>
       </c>
       <c r="D14" t="n">
-        <v>6.244200105843946</v>
+        <v>7.366583168724112</v>
       </c>
       <c r="E14" t="n">
-        <v>17.72304951830075</v>
+        <v>16.87497658146419</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.67375220853926</v>
+        <v>1.435246421269539</v>
       </c>
       <c r="C15" t="n">
-        <v>10.80201291019498</v>
+        <v>8.836563823769904</v>
       </c>
       <c r="D15" t="n">
-        <v>6.255774911277015</v>
+        <v>7.5312909810656</v>
       </c>
       <c r="E15" t="n">
-        <v>18.73154003001125</v>
+        <v>17.80310122610504</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.91384842708986</v>
+        <v>1.639793555449363</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81667700903394</v>
+        <v>10.56281989953228</v>
       </c>
       <c r="D16" t="n">
-        <v>6.730911347701344</v>
+        <v>8.19796639458848</v>
       </c>
       <c r="E16" t="n">
-        <v>21.46143678382514</v>
+        <v>20.40057984957012</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.518852055763198</v>
+        <v>1.295386643322539</v>
       </c>
       <c r="C17" t="n">
-        <v>11.84025037734415</v>
+        <v>9.89442642752697</v>
       </c>
       <c r="D17" t="n">
-        <v>6.227598752165131</v>
+        <v>7.732205648739709</v>
       </c>
       <c r="E17" t="n">
-        <v>19.58670118527248</v>
+        <v>18.92201871958922</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.705001237965436</v>
+        <v>1.453683643155295</v>
       </c>
       <c r="C18" t="n">
-        <v>13.81283676957909</v>
+        <v>11.66670683566444</v>
       </c>
       <c r="D18" t="n">
-        <v>6.591660253330977</v>
+        <v>8.291409141078692</v>
       </c>
       <c r="E18" t="n">
-        <v>22.10949826087551</v>
+        <v>21.41179961989842</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.683520598196516</v>
+        <v>1.434608285261779</v>
       </c>
       <c r="C19" t="n">
-        <v>14.74750967140727</v>
+        <v>12.60866430545813</v>
       </c>
       <c r="D19" t="n">
-        <v>6.672644621454297</v>
+        <v>8.465198119684462</v>
       </c>
       <c r="E19" t="n">
-        <v>23.10367489105808</v>
+        <v>22.50847071040437</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.847020860861779</v>
+        <v>1.570040381062627</v>
       </c>
       <c r="C20" t="n">
-        <v>16.82918786853812</v>
+        <v>14.54978568377196</v>
       </c>
       <c r="D20" t="n">
-        <v>7.093195885522502</v>
+        <v>8.963965223350012</v>
       </c>
       <c r="E20" t="n">
-        <v>25.7694046149224</v>
+        <v>25.0837912881846</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.081738707924348</v>
+        <v>0.9230391915328512</v>
       </c>
       <c r="C21" t="n">
-        <v>12.22247421103856</v>
+        <v>10.75969958414194</v>
       </c>
       <c r="D21" t="n">
-        <v>5.920007378947564</v>
+        <v>7.520167779576483</v>
       </c>
       <c r="E21" t="n">
-        <v>19.22422029791047</v>
+        <v>19.20290655525127</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_15_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248386881001325</v>
+        <v>2.615061246731673</v>
       </c>
       <c r="C3" t="n">
-        <v>4.604609663229524</v>
+        <v>7.711419219197309</v>
       </c>
       <c r="D3" t="n">
-        <v>6.193056053125848</v>
+        <v>8.1987495978093</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0460525973567</v>
+        <v>18.52523006373828</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.361261519737573</v>
+        <v>1.132757289466581</v>
       </c>
       <c r="C4" t="n">
-        <v>5.058195993700082</v>
+        <v>4.503311193974969</v>
       </c>
       <c r="D4" t="n">
-        <v>6.511907065912051</v>
+        <v>5.754484526235053</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93136457934971</v>
+        <v>11.3905530096766</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.515753976986745</v>
+        <v>1.286613542125511</v>
       </c>
       <c r="C5" t="n">
-        <v>5.613911787456547</v>
+        <v>5.147693539509944</v>
       </c>
       <c r="D5" t="n">
-        <v>6.872946848635062</v>
+        <v>6.067349089932391</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00261261307835</v>
+        <v>12.50165617156784</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.684635702008681</v>
+        <v>1.452004368172249</v>
       </c>
       <c r="C6" t="n">
-        <v>6.319497794675752</v>
+        <v>5.960293258661004</v>
       </c>
       <c r="D6" t="n">
-        <v>7.382701257708938</v>
+        <v>6.346378689587649</v>
       </c>
       <c r="E6" t="n">
-        <v>15.38683475439337</v>
+        <v>13.7586763164209</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.879883083389651</v>
+        <v>1.619242363373367</v>
       </c>
       <c r="C7" t="n">
-        <v>7.159556716972675</v>
+        <v>6.918866290363316</v>
       </c>
       <c r="D7" t="n">
-        <v>7.916481819011974</v>
+        <v>6.654363802858882</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9559216193743</v>
+        <v>15.19247245659557</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.119046003421087</v>
+        <v>1.802545410579416</v>
       </c>
       <c r="C8" t="n">
-        <v>4.82267820283136</v>
+        <v>8.029664954653128</v>
       </c>
       <c r="D8" t="n">
-        <v>6.171691336829056</v>
+        <v>6.9839415224354</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1134155430815</v>
+        <v>16.81615188766795</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.381155720613277</v>
+        <v>1.98204767078831</v>
       </c>
       <c r="C9" t="n">
-        <v>5.852181396561777</v>
+        <v>9.28507671094227</v>
       </c>
       <c r="D9" t="n">
-        <v>6.881097350875271</v>
+        <v>7.422421381915208</v>
       </c>
       <c r="E9" t="n">
-        <v>14.11443446805032</v>
+        <v>18.68954576364579</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.656901115559408</v>
+        <v>1.212664581762703</v>
       </c>
       <c r="C10" t="n">
-        <v>7.048126988456517</v>
+        <v>6.877770986779625</v>
       </c>
       <c r="D10" t="n">
-        <v>7.604633049674902</v>
+        <v>5.837049697938708</v>
       </c>
       <c r="E10" t="n">
-        <v>16.30966115369083</v>
+        <v>13.92748526648104</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.922675323960846</v>
+        <v>1.163479021779938</v>
       </c>
       <c r="C11" t="n">
-        <v>8.391252553998203</v>
+        <v>7.351375896785329</v>
       </c>
       <c r="D11" t="n">
-        <v>8.240671073489988</v>
+        <v>5.676632123064779</v>
       </c>
       <c r="E11" t="n">
-        <v>18.55459895144904</v>
+        <v>14.19148704163005</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.191729304459689</v>
+        <v>1.286874890726719</v>
       </c>
       <c r="C12" t="n">
-        <v>9.849763675611468</v>
+        <v>8.688211928181166</v>
       </c>
       <c r="D12" t="n">
-        <v>9.052723974763689</v>
+        <v>6.018241054234499</v>
       </c>
       <c r="E12" t="n">
-        <v>21.09421695483485</v>
+        <v>15.99332787314239</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.454548798934983</v>
+        <v>1.030815454505066</v>
       </c>
       <c r="C13" t="n">
-        <v>11.40906844343753</v>
+        <v>8.263213347012723</v>
       </c>
       <c r="D13" t="n">
-        <v>9.727246039231908</v>
+        <v>5.473086371543288</v>
       </c>
       <c r="E13" t="n">
-        <v>23.59086328160442</v>
+        <v>14.76711517306108</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.424780990742269</v>
+        <v>1.142489255863141</v>
       </c>
       <c r="C14" t="n">
-        <v>8.083612421997813</v>
+        <v>9.694729127006127</v>
       </c>
       <c r="D14" t="n">
-        <v>7.366583168724112</v>
+        <v>5.849616068553067</v>
       </c>
       <c r="E14" t="n">
-        <v>16.87497658146419</v>
+        <v>16.68683445142234</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.435246421269539</v>
+        <v>1.130492298917245</v>
       </c>
       <c r="C15" t="n">
-        <v>8.836563823769904</v>
+        <v>10.47949897187286</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5312909810656</v>
+        <v>5.895483321295478</v>
       </c>
       <c r="E15" t="n">
-        <v>17.80310122610504</v>
+        <v>17.50547459208558</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.639793555449363</v>
+        <v>1.248626000169263</v>
       </c>
       <c r="C16" t="n">
-        <v>10.56281989953228</v>
+        <v>12.27074674565637</v>
       </c>
       <c r="D16" t="n">
-        <v>8.19796639458848</v>
+        <v>6.285688763825416</v>
       </c>
       <c r="E16" t="n">
-        <v>20.40057984957012</v>
+        <v>19.80506150965105</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.295386643322539</v>
+        <v>0.7517143996647403</v>
       </c>
       <c r="C17" t="n">
-        <v>9.89442642752697</v>
+        <v>9.226150765246164</v>
       </c>
       <c r="D17" t="n">
-        <v>7.732205648739709</v>
+        <v>5.225558322871541</v>
       </c>
       <c r="E17" t="n">
-        <v>18.92201871958922</v>
+        <v>15.20342348778245</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.453683643155295</v>
+        <v>0.6032937817367076</v>
       </c>
       <c r="C18" t="n">
-        <v>11.66670683566444</v>
+        <v>8.264784143339519</v>
       </c>
       <c r="D18" t="n">
-        <v>8.291409141078692</v>
+        <v>4.752434469240917</v>
       </c>
       <c r="E18" t="n">
-        <v>21.41179961989842</v>
+        <v>13.62051239431714</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.434608285261779</v>
+        <v>0.7109424175073703</v>
       </c>
       <c r="C19" t="n">
-        <v>12.60866430545813</v>
+        <v>10.24599028041775</v>
       </c>
       <c r="D19" t="n">
-        <v>8.465198119684462</v>
+        <v>5.214258406795659</v>
       </c>
       <c r="E19" t="n">
-        <v>22.50847071040437</v>
+        <v>16.17119110472078</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.570040381062627</v>
+        <v>0.8089012034371169</v>
       </c>
       <c r="C20" t="n">
-        <v>14.54978568377196</v>
+        <v>12.32113003783832</v>
       </c>
       <c r="D20" t="n">
-        <v>8.963965223350012</v>
+        <v>5.709510853680006</v>
       </c>
       <c r="E20" t="n">
-        <v>25.0837912881846</v>
+        <v>18.83954209495544</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9230391915328512</v>
+        <v>0.8929388069206441</v>
       </c>
       <c r="C21" t="n">
-        <v>10.75969958414194</v>
+        <v>14.39615198553438</v>
       </c>
       <c r="D21" t="n">
-        <v>7.520167779576483</v>
+        <v>6.148155727937481</v>
       </c>
       <c r="E21" t="n">
-        <v>19.20290655525127</v>
+        <v>21.4372465203925</v>
       </c>
     </row>
   </sheetData>
